--- a/english_banjara_words.xlsx
+++ b/english_banjara_words.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Desktop\Major\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kesoj\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F5837AA-BB1B-4578-8D02-B0420C5D366F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FFB1A88C-91E3-49E3-B3D7-D7AF02F6E3A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2072" uniqueCount="1719">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2109" uniqueCount="1755">
   <si>
     <t>English</t>
   </si>
@@ -5177,6 +5177,114 @@
   </si>
   <si>
     <t>uT</t>
+  </si>
+  <si>
+    <t>Emotion</t>
+  </si>
+  <si>
+    <t>Happy Diwali, Pooja</t>
+  </si>
+  <si>
+    <t>Divali h bar Subhash</t>
+  </si>
+  <si>
+    <t>🎉 Joyful, Festive</t>
+  </si>
+  <si>
+    <t>Wish you the same</t>
+  </si>
+  <si>
+    <t>Tuni bhi divali h bar</t>
+  </si>
+  <si>
+    <t>😊 Warm, Friendly</t>
+  </si>
+  <si>
+    <t>How do you celebrate Diwali?</t>
+  </si>
+  <si>
+    <t>To divali habbana kyon aacharan kare chi?</t>
+  </si>
+  <si>
+    <t>🤔 Curious, Interested</t>
+  </si>
+  <si>
+    <t>We do Lakshmi Puja today</t>
+  </si>
+  <si>
+    <t>Ham aaj Lakshmi puja karacha</t>
+  </si>
+  <si>
+    <t>🙏 Devotional, Respectful</t>
+  </si>
+  <si>
+    <t>Tomorrow we offer Puja to our ancestors</t>
+  </si>
+  <si>
+    <t>Sawa ham riyar puja karacha</t>
+  </si>
+  <si>
+    <t>🕯️ Respectful, Traditional</t>
+  </si>
+  <si>
+    <t>Is it?</t>
+  </si>
+  <si>
+    <t>Hav ka</t>
+  </si>
+  <si>
+    <t>😯 Surprised, Interested</t>
+  </si>
+  <si>
+    <t>We do Lakshmi Puja and in the evening we burst crackers</t>
+  </si>
+  <si>
+    <t>Ham Lakshmi puja karacha an san jasi ham pataki mara</t>
+  </si>
+  <si>
+    <t>🎆 Excited, Cheerful</t>
+  </si>
+  <si>
+    <t>In Lambadi tradition, married girls do “Mera” ritual</t>
+  </si>
+  <si>
+    <t>Mera Banjara ma kawar choriya mera karacha</t>
+  </si>
+  <si>
+    <t>🧡 Cultural, Traditional</t>
+  </si>
+  <si>
+    <t>What is Mera?</t>
+  </si>
+  <si>
+    <t>Mera kato kai?</t>
+  </si>
+  <si>
+    <t>🤨 Curious, Learning</t>
+  </si>
+  <si>
+    <t>Unmarried girls hold diyas in hand and do prayers for everyone’s well-being</t>
+  </si>
+  <si>
+    <t>Kawar choriya deepa hate ma jalle se jini acho vedken puja karacha</t>
+  </si>
+  <si>
+    <t>🕯️🙏 Caring, Blessing</t>
+  </si>
+  <si>
+    <t>Oh is it?</t>
+  </si>
+  <si>
+    <t>😌 Acknowledging</t>
+  </si>
+  <si>
+    <t>Okay, now I have to go home. Do come home</t>
+  </si>
+  <si>
+    <t>Sari ama ghar janu, ghare aa</t>
+  </si>
+  <si>
+    <t>🏡 Polite, Friendly</t>
   </si>
 </sst>
 </file>
@@ -5235,7 +5343,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -5245,6 +5353,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5550,22 +5662,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B1052"/>
+  <dimension ref="A1:C1052"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="28.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C1" s="4" t="s">
+        <v>1719</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -5573,7 +5688,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -5581,7 +5696,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -5589,7 +5704,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -5597,7 +5712,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -5605,7 +5720,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -5613,7 +5728,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -5621,7 +5736,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -5629,7 +5744,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -5637,7 +5752,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -5645,7 +5760,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -5653,7 +5768,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -5661,7 +5776,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -5669,7 +5784,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -5677,7 +5792,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -13749,7 +13864,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="1025" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1025" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1025" s="2" t="s">
         <v>108</v>
       </c>
@@ -13757,7 +13872,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="1026" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1026" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1026" s="2" t="s">
         <v>1640</v>
       </c>
@@ -13765,7 +13880,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="1027" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1027" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1027" s="2" t="s">
         <v>1564</v>
       </c>
@@ -13773,7 +13888,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="1028" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1028" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1028" s="2" t="s">
         <v>1638</v>
       </c>
@@ -13781,7 +13896,7 @@
         <v>1639</v>
       </c>
     </row>
-    <row r="1029" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1029" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1029" s="2" t="s">
         <v>1702</v>
       </c>
@@ -13789,7 +13904,7 @@
         <v>1703</v>
       </c>
     </row>
-    <row r="1030" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1030" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1030" s="2" t="s">
         <v>1562</v>
       </c>
@@ -13797,7 +13912,7 @@
         <v>1704</v>
       </c>
     </row>
-    <row r="1031" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1031" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1031" s="2" t="s">
         <v>1705</v>
       </c>
@@ -13805,7 +13920,7 @@
         <v>1706</v>
       </c>
     </row>
-    <row r="1032" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1032" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1032" s="2" t="s">
         <v>1707</v>
       </c>
@@ -13813,7 +13928,7 @@
         <v>1708</v>
       </c>
     </row>
-    <row r="1033" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1033" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1033" s="2" t="s">
         <v>1709</v>
       </c>
@@ -13821,7 +13936,7 @@
         <v>1710</v>
       </c>
     </row>
-    <row r="1034" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1034" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1034" s="2" t="s">
         <v>1711</v>
       </c>
@@ -13829,7 +13944,7 @@
         <v>1712</v>
       </c>
     </row>
-    <row r="1035" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1035" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1035" s="2" t="s">
         <v>1713</v>
       </c>
@@ -13837,7 +13952,7 @@
         <v>1714</v>
       </c>
     </row>
-    <row r="1036" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1036" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1036" s="2" t="s">
         <v>1715</v>
       </c>
@@ -13845,7 +13960,7 @@
         <v>1716</v>
       </c>
     </row>
-    <row r="1037" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1037" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1037" s="2" t="s">
         <v>1717</v>
       </c>
@@ -13853,63 +13968,148 @@
         <v>1718</v>
       </c>
     </row>
-    <row r="1038" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1038" s="2"/>
-      <c r="B1038" s="2"/>
-    </row>
-    <row r="1039" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1039" s="2"/>
-      <c r="B1039" s="2"/>
-    </row>
-    <row r="1040" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1040" s="2"/>
-      <c r="B1040" s="2"/>
-    </row>
-    <row r="1041" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1041" s="2"/>
-      <c r="B1041" s="2"/>
-    </row>
-    <row r="1042" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1042" s="2"/>
-      <c r="B1042" s="2"/>
-    </row>
-    <row r="1043" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1043" s="2"/>
-      <c r="B1043" s="2"/>
-    </row>
-    <row r="1044" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1044" s="2"/>
-      <c r="B1044" s="2"/>
-    </row>
-    <row r="1045" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1045" s="2"/>
-      <c r="B1045" s="2"/>
-    </row>
-    <row r="1046" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1046" s="2"/>
-      <c r="B1046" s="2"/>
-    </row>
-    <row r="1047" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1047" s="2"/>
-      <c r="B1047" s="2"/>
-    </row>
-    <row r="1048" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1048" s="2"/>
-      <c r="B1048" s="2"/>
-    </row>
-    <row r="1049" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1049" s="2"/>
-      <c r="B1049" s="2"/>
-    </row>
-    <row r="1050" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1050" s="2"/>
-      <c r="B1050" s="2"/>
-    </row>
-    <row r="1051" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1038" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1038" s="5"/>
+      <c r="B1038" s="5"/>
+      <c r="C1038" s="5"/>
+    </row>
+    <row r="1039" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A1039" s="2" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B1039" s="2" t="s">
+        <v>1721</v>
+      </c>
+      <c r="C1039" s="2" t="s">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A1040" s="2" t="s">
+        <v>1723</v>
+      </c>
+      <c r="B1040" s="2" t="s">
+        <v>1724</v>
+      </c>
+      <c r="C1040" s="2" t="s">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A1041" s="2" t="s">
+        <v>1726</v>
+      </c>
+      <c r="B1041" s="2" t="s">
+        <v>1727</v>
+      </c>
+      <c r="C1041" s="2" t="s">
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:3" ht="72" x14ac:dyDescent="0.3">
+      <c r="A1042" s="2" t="s">
+        <v>1729</v>
+      </c>
+      <c r="B1042" s="2" t="s">
+        <v>1730</v>
+      </c>
+      <c r="C1042" s="2" t="s">
+        <v>1731</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:3" ht="72" x14ac:dyDescent="0.3">
+      <c r="A1043" s="2" t="s">
+        <v>1732</v>
+      </c>
+      <c r="B1043" s="2" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C1043" s="2" t="s">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:3" ht="72" x14ac:dyDescent="0.3">
+      <c r="A1044" s="2" t="s">
+        <v>1735</v>
+      </c>
+      <c r="B1044" s="2" t="s">
+        <v>1736</v>
+      </c>
+      <c r="C1044" s="2" t="s">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A1045" s="2" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B1045" s="2" t="s">
+        <v>1739</v>
+      </c>
+      <c r="C1045" s="2" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A1046" s="2" t="s">
+        <v>1741</v>
+      </c>
+      <c r="B1046" s="2" t="s">
+        <v>1742</v>
+      </c>
+      <c r="C1046" s="2" t="s">
+        <v>1743</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A1047" s="2" t="s">
+        <v>1744</v>
+      </c>
+      <c r="B1047" s="2" t="s">
+        <v>1745</v>
+      </c>
+      <c r="C1047" s="2" t="s">
+        <v>1746</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A1048" s="2" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B1048" s="2" t="s">
+        <v>1748</v>
+      </c>
+      <c r="C1048" s="2" t="s">
+        <v>1749</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A1049" s="2" t="s">
+        <v>1750</v>
+      </c>
+      <c r="B1049" s="2" t="s">
+        <v>1736</v>
+      </c>
+      <c r="C1049" s="2" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A1050" s="2" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B1050" s="2" t="s">
+        <v>1753</v>
+      </c>
+      <c r="C1050" s="2" t="s">
+        <v>1754</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1051" s="2"/>
       <c r="B1051" s="2"/>
     </row>
-    <row r="1052" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1052" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1052" s="2"/>
       <c r="B1052" s="2"/>
     </row>
